--- a/public/ejemplo-picas.xlsx
+++ b/public/ejemplo-picas.xlsx
@@ -468,7 +468,7 @@
         <v>470341.4</v>
       </c>
       <c r="F2">
-        <v>6969156.99</v>
+        <v>6969159.04</v>
       </c>
       <c r="G2">
         <v>470341.56</v>
@@ -503,10 +503,10 @@
         <v>470347.4</v>
       </c>
       <c r="F3">
-        <v>6969157.01</v>
+        <v>6969159.06</v>
       </c>
       <c r="G3">
-        <v>470347.57</v>
+        <v>470347.56</v>
       </c>
       <c r="H3" t="str">
         <v>Norte</v>
@@ -538,10 +538,10 @@
         <v>470353.41</v>
       </c>
       <c r="F4">
-        <v>6969157.02</v>
+        <v>6969159.07</v>
       </c>
       <c r="G4">
-        <v>470353.57</v>
+        <v>470353.56</v>
       </c>
       <c r="H4" t="str">
         <v>Norte</v>
@@ -573,10 +573,10 @@
         <v>470359.41</v>
       </c>
       <c r="F5">
-        <v>6969157.03</v>
+        <v>6969159.09</v>
       </c>
       <c r="G5">
-        <v>470359.57</v>
+        <v>470359.56</v>
       </c>
       <c r="H5" t="str">
         <v>Norte</v>
@@ -608,7 +608,7 @@
         <v>470365.41</v>
       </c>
       <c r="F6">
-        <v>6969157.05</v>
+        <v>6969159.1</v>
       </c>
       <c r="G6">
         <v>470365.57</v>
@@ -643,7 +643,7 @@
         <v>470371.41</v>
       </c>
       <c r="F7">
-        <v>6969157.06</v>
+        <v>6969159.12</v>
       </c>
       <c r="G7">
         <v>470371.57</v>
@@ -678,7 +678,7 @@
         <v>470377.41</v>
       </c>
       <c r="F8">
-        <v>6969157.08</v>
+        <v>6969159.13</v>
       </c>
       <c r="G8">
         <v>470377.57</v>
@@ -713,10 +713,10 @@
         <v>470383.42</v>
       </c>
       <c r="F9">
-        <v>6969157.09</v>
+        <v>6969159.14</v>
       </c>
       <c r="G9">
-        <v>470383.58</v>
+        <v>470383.57</v>
       </c>
       <c r="H9" t="str">
         <v>Norte</v>
@@ -748,10 +748,10 @@
         <v>470389.42</v>
       </c>
       <c r="F10">
-        <v>6969157.11</v>
+        <v>6969159.16</v>
       </c>
       <c r="G10">
-        <v>470389.58</v>
+        <v>470389.57</v>
       </c>
       <c r="H10" t="str">
         <v>Norte</v>
@@ -783,7 +783,7 @@
         <v>470395.42</v>
       </c>
       <c r="F11">
-        <v>6969157.12</v>
+        <v>6969159.17</v>
       </c>
       <c r="G11">
         <v>470395.58</v>
@@ -818,7 +818,7 @@
         <v>470401.42</v>
       </c>
       <c r="F12">
-        <v>6969157.14</v>
+        <v>6969159.19</v>
       </c>
       <c r="G12">
         <v>470401.58</v>
@@ -853,7 +853,7 @@
         <v>470407.42</v>
       </c>
       <c r="F13">
-        <v>6969157.15</v>
+        <v>6969159.2</v>
       </c>
       <c r="G13">
         <v>470407.58</v>
@@ -882,16 +882,16 @@
         <v>R1</v>
       </c>
       <c r="D14">
-        <v>6969149</v>
+        <v>6969151.06</v>
       </c>
       <c r="E14">
         <v>470341.58</v>
       </c>
       <c r="F14">
-        <v>6969081.91</v>
+        <v>6969086.02</v>
       </c>
       <c r="G14">
-        <v>470341.74</v>
+        <v>470341.73</v>
       </c>
       <c r="H14" t="str">
         <v>Sur</v>
@@ -917,16 +917,16 @@
         <v>R1</v>
       </c>
       <c r="D15">
-        <v>6969149.02</v>
+        <v>6969151.07</v>
       </c>
       <c r="E15">
-        <v>470347.59</v>
+        <v>470347.58</v>
       </c>
       <c r="F15">
-        <v>6969081.93</v>
+        <v>6969086.03</v>
       </c>
       <c r="G15">
-        <v>470347.75</v>
+        <v>470347.74</v>
       </c>
       <c r="H15" t="str">
         <v>Sur</v>
@@ -952,16 +952,16 @@
         <v>R1</v>
       </c>
       <c r="D16">
-        <v>6969149.03</v>
+        <v>6969151.08</v>
       </c>
       <c r="E16">
-        <v>470353.59</v>
+        <v>470353.58</v>
       </c>
       <c r="F16">
-        <v>6969081.94</v>
+        <v>6969086.05</v>
       </c>
       <c r="G16">
-        <v>470353.75</v>
+        <v>470353.74</v>
       </c>
       <c r="H16" t="str">
         <v>Sur</v>
@@ -987,16 +987,16 @@
         <v>R1</v>
       </c>
       <c r="D17">
-        <v>6969149.05</v>
+        <v>6969151.1</v>
       </c>
       <c r="E17">
-        <v>470359.59</v>
+        <v>470359.58</v>
       </c>
       <c r="F17">
-        <v>6969081.96</v>
+        <v>6969086.06</v>
       </c>
       <c r="G17">
-        <v>470359.75</v>
+        <v>470359.74</v>
       </c>
       <c r="H17" t="str">
         <v>Sur</v>
@@ -1022,16 +1022,16 @@
         <v>R1</v>
       </c>
       <c r="D18">
-        <v>6969149.06</v>
+        <v>6969151.11</v>
       </c>
       <c r="E18">
         <v>470365.59</v>
       </c>
       <c r="F18">
-        <v>6969081.97</v>
+        <v>6969086.07</v>
       </c>
       <c r="G18">
-        <v>470365.75</v>
+        <v>470365.74</v>
       </c>
       <c r="H18" t="str">
         <v>Sur</v>
@@ -1057,16 +1057,16 @@
         <v>R1</v>
       </c>
       <c r="D19">
-        <v>6969149.08</v>
+        <v>6969151.13</v>
       </c>
       <c r="E19">
         <v>470371.59</v>
       </c>
       <c r="F19">
-        <v>6969081.99</v>
+        <v>6969086.09</v>
       </c>
       <c r="G19">
-        <v>470371.75</v>
+        <v>470371.74</v>
       </c>
       <c r="H19" t="str">
         <v>Sur</v>
@@ -1092,16 +1092,16 @@
         <v>R1</v>
       </c>
       <c r="D20">
-        <v>6969149.09</v>
+        <v>6969151.14</v>
       </c>
       <c r="E20">
         <v>470377.59</v>
       </c>
       <c r="F20">
-        <v>6969082</v>
+        <v>6969086.1</v>
       </c>
       <c r="G20">
-        <v>470377.76</v>
+        <v>470377.75</v>
       </c>
       <c r="H20" t="str">
         <v>Sur</v>
@@ -1127,16 +1127,16 @@
         <v>R1</v>
       </c>
       <c r="D21">
-        <v>6969149.11</v>
+        <v>6969151.16</v>
       </c>
       <c r="E21">
-        <v>470383.6</v>
+        <v>470383.59</v>
       </c>
       <c r="F21">
-        <v>6969082.01</v>
+        <v>6969086.12</v>
       </c>
       <c r="G21">
-        <v>470383.76</v>
+        <v>470383.75</v>
       </c>
       <c r="H21" t="str">
         <v>Sur</v>
@@ -1162,16 +1162,16 @@
         <v>R1</v>
       </c>
       <c r="D22">
-        <v>6969149.12</v>
+        <v>6969151.17</v>
       </c>
       <c r="E22">
-        <v>470389.6</v>
+        <v>470389.59</v>
       </c>
       <c r="F22">
-        <v>6969082.03</v>
+        <v>6969086.13</v>
       </c>
       <c r="G22">
-        <v>470389.76</v>
+        <v>470389.75</v>
       </c>
       <c r="H22" t="str">
         <v>Sur</v>
@@ -1197,16 +1197,16 @@
         <v>R1</v>
       </c>
       <c r="D23">
-        <v>6969149.13</v>
+        <v>6969151.19</v>
       </c>
       <c r="E23">
-        <v>470395.6</v>
+        <v>470395.59</v>
       </c>
       <c r="F23">
-        <v>6969082.04</v>
+        <v>6969086.15</v>
       </c>
       <c r="G23">
-        <v>470395.76</v>
+        <v>470395.75</v>
       </c>
       <c r="H23" t="str">
         <v>Sur</v>
@@ -1232,16 +1232,16 @@
         <v>R1</v>
       </c>
       <c r="D24">
-        <v>6969149.15</v>
+        <v>6969151.2</v>
       </c>
       <c r="E24">
         <v>470401.6</v>
       </c>
       <c r="F24">
-        <v>6969082.06</v>
+        <v>6969086.16</v>
       </c>
       <c r="G24">
-        <v>470401.76</v>
+        <v>470401.75</v>
       </c>
       <c r="H24" t="str">
         <v>Sur</v>
@@ -1267,16 +1267,16 @@
         <v>R1</v>
       </c>
       <c r="D25">
-        <v>6969149.16</v>
+        <v>6969151.21</v>
       </c>
       <c r="E25">
         <v>470407.6</v>
       </c>
       <c r="F25">
-        <v>6969082.07</v>
+        <v>6969086.18</v>
       </c>
       <c r="G25">
-        <v>470407.76</v>
+        <v>470407.75</v>
       </c>
       <c r="H25" t="str">
         <v>Sur</v>
